--- a/en/downloads/data-excel/1.2.1.xlsx
+++ b/en/downloads/data-excel/1.2.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF852D56-D485-4A55-BE9D-DA114B4AEE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="5385" windowHeight="3435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -247,7 +248,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -418,7 +419,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -426,103 +427,32 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -530,15 +460,46 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="2"/>
-    <cellStyle name="Обычный 3" xfId="3"/>
-    <cellStyle name="Обычный 4" xfId="6"/>
-    <cellStyle name="Процентный 2" xfId="5"/>
-    <cellStyle name="Процентный 3" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Процентный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Процентный 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -554,9 +515,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -594,9 +555,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -631,7 +592,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -666,7 +627,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -839,8 +800,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" customWidth="1"/>
@@ -848,606 +809,631 @@
     <col min="3" max="3" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="8" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>2007</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>2008</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>2009</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <v>2010</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="11">
         <v>2011</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="11">
         <v>2012</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="11">
         <v>2013</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="11">
         <v>2014</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="11">
         <v>2015</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="11">
         <v>2016</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="11">
         <v>2017</v>
       </c>
-      <c r="O4" s="15">
+      <c r="O4" s="11">
         <v>2018</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4" s="11">
         <v>2019</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="11">
         <v>2020</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="11">
         <v>2021</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="11">
         <v>2022</v>
       </c>
-      <c r="T4" s="15">
+      <c r="T4" s="11">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="U4" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="19">
         <v>35</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="19">
         <v>31.7</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="19">
         <v>31.7</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="19">
         <v>33.700000000000003</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="19">
         <v>36.799999999999997</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="19">
         <v>38</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="19">
         <v>37</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="19">
         <v>30.6</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="19">
         <v>32.1</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="19">
         <v>25.4</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="19">
         <v>25.6</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="19">
         <v>22.4</v>
       </c>
-      <c r="P5" s="25">
+      <c r="P5" s="19">
         <v>20.124198474961176</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="19">
         <v>25.3</v>
       </c>
-      <c r="R5" s="25">
+      <c r="R5" s="19">
         <v>33.262233298138462</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="19">
         <v>33.152856050161155</v>
       </c>
-      <c r="T5" s="25">
+      <c r="T5" s="19">
         <v>29.810232786618478</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="U5" s="19">
+        <v>25.693838345903199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>34.700000000000003</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>31.4</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="12">
         <v>30.7</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="12">
         <v>32.700000000000003</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="12">
         <v>36.1</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="12">
         <v>37.200000000000003</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="12">
         <v>36.5</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <v>29.7</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="12">
         <v>31.5</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="12">
         <v>25</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="12">
         <v>25</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="12">
         <v>22.5</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="12">
         <v>20.078519398883305</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="12">
         <v>25.3</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="12">
         <v>33.10733359588</v>
       </c>
-      <c r="S7" s="37">
+      <c r="S7" s="12">
         <v>32.831913512166025</v>
       </c>
-      <c r="T7" s="37">
+      <c r="T7" s="12">
         <v>29.669466599025686</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="U7" s="12">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="12">
         <v>35.4</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="12">
         <v>32.1</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="12">
         <v>32.9</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="12">
         <v>34.799999999999997</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="12">
         <v>37.6</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="12">
         <v>39</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="12">
         <v>37.5</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <v>31.5</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="12">
         <v>32.700000000000003</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="12">
         <v>25.7</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="12">
         <v>26.3</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="12">
         <v>22.2</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="12">
         <v>20.175708173042036</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="12">
         <v>25.3</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="12">
         <v>33.434791912906064</v>
       </c>
-      <c r="S8" s="37">
+      <c r="S8" s="12">
         <v>33.509346380994529</v>
       </c>
-      <c r="T8" s="37">
+      <c r="T8" s="12">
         <v>29.964546620904322</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="U8" s="12">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="12">
         <v>23.2</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="12">
         <v>22.6</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="12">
         <v>21.9</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="12">
         <v>23.6</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="12">
         <v>30.7</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="12">
         <v>35.4</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="12">
         <v>28.5</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <v>26.9</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="12">
         <v>29.3</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="12">
         <v>18.600000000000001</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="12">
         <v>20.399999999999999</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="12">
         <v>20.100000000000001</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="12">
         <v>14.7</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="12">
         <v>18.3</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="12">
         <v>33.257744153601877</v>
       </c>
-      <c r="S10" s="37">
+      <c r="S10" s="12">
         <v>34.041194942162896</v>
       </c>
-      <c r="T10" s="37">
+      <c r="T10" s="12">
         <v>30.196132774743152</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="U10" s="12">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <v>41.7</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>36.799999999999997</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="12">
         <v>37.1</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <v>39.5</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="12">
         <v>40.4</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="12">
         <v>39.6</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="12">
         <v>41.4</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <v>32.6</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="12">
         <v>33.6</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="12">
         <v>29</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="12">
         <v>28.4</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="12">
         <v>23.7</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="12">
         <v>23.2</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="12">
         <v>29.3</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="12">
         <v>33.264901349775037</v>
       </c>
-      <c r="S11" s="37">
+      <c r="S11" s="12">
         <v>32.636018013483323</v>
       </c>
-      <c r="T11" s="37">
+      <c r="T11" s="12">
         <v>29.586576623908091</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="U11" s="12">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="12">
         <v>45.2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <v>37.9</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="12">
         <v>40.5</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="12">
         <v>31.5</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="12">
         <v>32</v>
       </c>
-      <c r="O13" s="16">
+      <c r="O13" s="12">
         <v>28.3</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="12">
         <v>25.7</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="12">
         <v>31.8</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="12">
         <v>40.506761643955343</v>
       </c>
-      <c r="S13" s="37">
+      <c r="S13" s="12">
         <v>40.271414365477746</v>
       </c>
-      <c r="T13" s="37">
+      <c r="T13" s="12">
         <v>36.679314997357302</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="U13" s="12">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="12">
         <v>35.6</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <v>28.5</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="12">
         <v>29</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="12">
         <v>23</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="12">
         <v>22.9</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="12">
         <v>20.9</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="12">
         <v>16.2</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="12">
         <v>22</v>
       </c>
-      <c r="R14" s="16">
+      <c r="R14" s="12">
         <v>31.172874511993772</v>
       </c>
-      <c r="S14" s="37">
+      <c r="S14" s="12">
         <v>31.568157010024336</v>
       </c>
-      <c r="T14" s="37">
+      <c r="T14" s="12">
         <v>27.761651579699627</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U14" s="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
@@ -1457,59 +1443,62 @@
       <c r="C15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="12">
         <v>33.299999999999997</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <v>27</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="12">
         <v>27.9</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="12">
         <v>21.8</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="12">
         <v>22</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="12">
         <v>19.3</v>
       </c>
-      <c r="P15" s="16">
+      <c r="P15" s="12">
         <v>17.117237487541317</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="Q15" s="12">
         <v>21.7</v>
       </c>
-      <c r="R15" s="16">
+      <c r="R15" s="12">
         <v>29.650854888195603</v>
       </c>
-      <c r="S15" s="37">
+      <c r="S15" s="12">
         <v>30.277813022272248</v>
       </c>
-      <c r="T15" s="37">
+      <c r="T15" s="12">
         <v>26.945499612171261</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U15" s="12">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
@@ -1519,333 +1508,348 @@
       <c r="C16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="12">
         <v>25.2</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <v>21.3</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="12">
         <v>21.8</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="12">
         <v>19.899999999999999</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="12">
         <v>18.899999999999999</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="12">
         <v>14.8</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="12">
         <v>13.285423782570058</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="12">
         <v>17.8</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="12">
         <v>24.097659040517694</v>
       </c>
-      <c r="S16" s="37">
+      <c r="S16" s="12">
         <v>22.733608300917229</v>
       </c>
-      <c r="T16" s="37">
+      <c r="T16" s="12">
         <v>19.920707357966336</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="U16" s="12">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="12">
         <v>40.402479889759874</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>20.741559677258106</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="12">
         <v>31.472533233133365</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="12">
         <v>33.595651944803727</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="12">
         <v>35.637925280764073</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="12">
         <v>34.235279979054241</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="12">
         <v>53.855810041406322</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <v>40.719691825525814</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="12">
         <v>41.156482988237698</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="12">
         <v>37.049867142684406</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="12">
         <v>40.518930421912231</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="12">
         <v>33.773947202914634</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="12">
         <v>32.60027766870374</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="12">
         <v>34.700000000000003</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="12">
         <v>40.671537678982844</v>
       </c>
-      <c r="S18" s="37">
+      <c r="S18" s="12">
         <v>48.492370829119814</v>
       </c>
-      <c r="T18" s="37">
+      <c r="T18" s="12">
         <v>48.132487638243802</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="U18" s="12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="12">
         <v>41.298197061272944</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>22.400606661789254</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="12">
         <v>31.273920861021736</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="12">
         <v>31.928277981030423</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="12">
         <v>34.181401408145312</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="12">
         <v>34.639723309128705</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="12">
         <v>53.627066611694964</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <v>39.011011201209385</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="12">
         <v>40.926453617457369</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="12">
         <v>36.116546796954033</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="12">
         <v>39.604539591896497</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="12">
         <v>33.671053924880781</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="12">
         <v>32.424873967888452</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="12">
         <v>34.299999999999997</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="12">
         <v>40.835744431591088</v>
       </c>
-      <c r="S19" s="37">
+      <c r="S19" s="12">
         <v>46.987664282528065</v>
       </c>
-      <c r="T19" s="37">
+      <c r="T19" s="12">
         <v>47.095468608697217</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="U19" s="12">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="12">
         <v>39.381263817790511</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>18.757342571657283</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="12">
         <v>31.703884845676683</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="12">
         <v>35.55793402205002</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="12">
         <v>37.347648282219502</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="12">
         <v>33.764476225800678</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="12">
         <v>54.08783910774202</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="12">
         <v>42.448702330320252</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="12">
         <v>41.395881762864036</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="12">
         <v>38.033368857397804</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="12">
         <v>41.521176404727939</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="12">
         <v>33.888978930781725</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="12">
         <v>32.794370380144969</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="12">
         <v>35.1</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="12">
         <v>40.494322790314847</v>
       </c>
-      <c r="S20" s="37">
+      <c r="S20" s="12">
         <v>50.118899291215271</v>
       </c>
-      <c r="T20" s="37">
+      <c r="T20" s="12">
         <v>49.224436679851941</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="U20" s="12">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="12">
         <v>53.037853145464332</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>40.086270531670472</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="12">
         <v>36.873144430974918</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="12">
         <v>44.705496370584875</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="12">
         <v>45.290428057708084</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="12">
         <v>55.657830690086428</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="12">
         <v>46.41253835816282</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="12">
         <v>46.435379481648589</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="12">
         <v>45.092334897269765</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="12">
         <v>32.247345241286098</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="12">
         <v>32.580650410531696</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="12">
         <v>32.215180398381278</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="12">
         <v>26.949229229116593</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="12">
         <v>37.200000000000003</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="12">
         <v>43.213901910043809</v>
       </c>
-      <c r="S21" s="37">
+      <c r="S21" s="12">
         <v>47.142900749295329</v>
       </c>
-      <c r="T21" s="37">
+      <c r="T21" s="12">
         <v>36.060409324309092</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="12">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
@@ -1855,1489 +1859,1558 @@
       <c r="C22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="12">
         <v>51.581913300980112</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>37.898730956037639</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="12">
         <v>33.475026855982897</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="12">
         <v>43.666947672535464</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="12">
         <v>43.691713616679245</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="12">
         <v>55.271782333465687</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="12">
         <v>47.356835988795638</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="12">
         <v>47.010504519675102</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="12">
         <v>45.246248393795341</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="12">
         <v>33.070935081614579</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="12">
         <v>33.991287702261047</v>
       </c>
-      <c r="O22" s="16">
+      <c r="O22" s="12">
         <v>33.427506155728132</v>
       </c>
-      <c r="P22" s="16">
+      <c r="P22" s="12">
         <v>27.837054029315262</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="Q22" s="12">
         <v>39</v>
       </c>
-      <c r="R22" s="16">
+      <c r="R22" s="12">
         <v>43.25339669708363</v>
       </c>
-      <c r="S22" s="37">
+      <c r="S22" s="12">
         <v>47.199946558584017</v>
       </c>
-      <c r="T22" s="37">
+      <c r="T22" s="12">
         <v>36.438841751655779</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="U22" s="12">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="12">
         <v>54.569085687052358</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="12">
         <v>42.427936426011655</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="12">
         <v>40.528056096234025</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="12">
         <v>45.762935658295987</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="12">
         <v>46.925945902420438</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="12">
         <v>56.050612838025486</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="12">
         <v>45.459523948653484</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="12">
         <v>45.842337649953734</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="12">
         <v>44.933484159094526</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="12">
         <v>31.382457734244912</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="12">
         <v>31.110381241015197</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="12">
         <v>30.92489536681844</v>
       </c>
-      <c r="P23" s="16">
+      <c r="P23" s="12">
         <v>26.006375104165304</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="Q23" s="12">
         <v>35.4</v>
       </c>
-      <c r="R23" s="16">
+      <c r="R23" s="12">
         <v>43.172054336673064</v>
       </c>
-      <c r="S23" s="37">
+      <c r="S23" s="12">
         <v>47.082025761639336</v>
       </c>
-      <c r="T23" s="37">
+      <c r="T23" s="12">
         <v>35.670056408825062</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="U23" s="12">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="12">
         <v>38.587156397141321</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="12">
         <v>52.243735659060569</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="12">
         <v>46.090373783194451</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="12">
         <v>38.013539204566712</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="12">
         <v>29.522754727724266</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="12">
         <v>28.137635133798742</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="12">
         <v>39.477989961494835</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="12">
         <v>26.014325183400164</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="12">
         <v>28.892638246691408</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="12">
         <v>24.74455342190311</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="12">
         <v>24.170328861189912</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="12">
         <v>21.529510496448221</v>
       </c>
-      <c r="P24" s="16">
+      <c r="P24" s="12">
         <v>24.449709453745115</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="Q24" s="12">
         <v>27.9</v>
       </c>
-      <c r="R24" s="16">
+      <c r="R24" s="12">
         <v>38.130315382405762</v>
       </c>
-      <c r="S24" s="37">
+      <c r="S24" s="12">
         <v>31.240016364696597</v>
       </c>
-      <c r="T24" s="37">
+      <c r="T24" s="12">
         <v>30.852411825788565</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="U24" s="12">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="12">
         <v>38.684593590774618</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="12">
         <v>52.152947022826481</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="12">
         <v>47.889059425246316</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="12">
         <v>36.910698798507255</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="12">
         <v>31.115103240448146</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="12">
         <v>28.242617789669175</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="12">
         <v>40.426190005675039</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="12">
         <v>26.3548130266553</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="12">
         <v>29.078560303070596</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="12">
         <v>24.749641705183127</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="12">
         <v>24.266813149633116</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O25" s="12">
         <v>21.495640575964732</v>
       </c>
-      <c r="P25" s="16">
+      <c r="P25" s="12">
         <v>25.261407984004691</v>
       </c>
-      <c r="Q25" s="16">
+      <c r="Q25" s="12">
         <v>29</v>
       </c>
-      <c r="R25" s="16">
+      <c r="R25" s="12">
         <v>39.052986923894757</v>
       </c>
-      <c r="S25" s="37">
+      <c r="S25" s="12">
         <v>31.228685777194666</v>
       </c>
-      <c r="T25" s="37">
+      <c r="T25" s="12">
         <v>30.330534800771165</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="U25" s="12">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="12">
         <v>38.498842893622495</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="12">
         <v>52.320360206669946</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="12">
         <v>44.512909658620337</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="12">
         <v>39.00628927384588</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="12">
         <v>28.11224725260351</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="12">
         <v>28.021324105956992</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="12">
         <v>38.474804276820919</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="12">
         <v>25.663078513514154</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="12">
         <v>28.701454292915692</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="12">
         <v>24.739204448529353</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="12">
         <v>24.067406584555748</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="12">
         <v>21.566132496570411</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="12">
         <v>23.571244210416801</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="12">
         <v>26.7</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="12">
         <v>37.162402419999459</v>
       </c>
-      <c r="S26" s="37">
+      <c r="S26" s="12">
         <v>31.252112297543153</v>
       </c>
-      <c r="T26" s="37">
+      <c r="T26" s="12">
         <v>31.403214482728419</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="U26" s="12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="12">
         <v>45.182678649814314</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="12">
         <v>42.730283811653365</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="12">
         <v>44.117919691307137</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="12">
         <v>53.531335146815451</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="12">
         <v>49.925097790099393</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="12">
         <v>39.932299240936274</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="12">
         <v>43.754395294404411</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="12">
         <v>30.560926744429675</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="12">
         <v>38.007028694030566</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="12">
         <v>37.79821150847107</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="12">
         <v>29.21833950434447</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="12">
         <v>30.596327932893466</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="12">
         <v>28.138697667467131</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="12">
         <v>36.799999999999997</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="12">
         <v>39.151777291250745</v>
       </c>
-      <c r="S27" s="37">
+      <c r="S27" s="12">
         <v>42.049857693482664</v>
       </c>
-      <c r="T27" s="37">
+      <c r="T27" s="12">
         <v>38.094443042646382</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="U27" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="12">
         <v>46.868158500298755</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="12">
         <v>42.698866213804251</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="12">
         <v>44.838863302106681</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="12">
         <v>53.397508505190693</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="12">
         <v>48.269823904649712</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="12">
         <v>37.664069415042029</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="12">
         <v>44.781414591166033</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="12">
         <v>32.369300618626895</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="12">
         <v>39.504743553298205</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="12">
         <v>39.601891368837386</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="12">
         <v>31.189138362275092</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="12">
         <v>31.594899662350688</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="12">
         <v>28.978045168904039</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="12">
         <v>37.6</v>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="12">
         <v>39.257524172776719</v>
       </c>
-      <c r="S28" s="37">
+      <c r="S28" s="12">
         <v>42.689244289315013</v>
       </c>
-      <c r="T28" s="37">
+      <c r="T28" s="12">
         <v>38.158675127516169</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="U28" s="12">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="12">
         <v>43.678264522994652</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="12">
         <v>42.757724565987253</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="12">
         <v>43.49630815436538</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="12">
         <v>53.676667578832138</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="12">
         <v>51.7285367396859</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="12">
         <v>42.395906143747297</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="12">
         <v>42.671843342389494</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="12">
         <v>28.643083188639221</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="12">
         <v>36.407724820754808</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="12">
         <v>35.859946286618936</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="12">
         <v>27.069804008596218</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="12">
         <v>29.460632166824883</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="12">
         <v>27.215175085071412</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="12">
         <v>35.9</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="12">
         <v>39.034895273433577</v>
       </c>
-      <c r="S29" s="37">
+      <c r="S29" s="12">
         <v>41.380596558931735</v>
       </c>
-      <c r="T29" s="37">
+      <c r="T29" s="12">
         <v>38.024712001344874</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="U29" s="12">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="12">
         <v>46.591609930340859</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="12">
         <v>37.452826077173327</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="12">
         <v>38.292035961047127</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="12">
         <v>41.897117973076092</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="12">
         <v>44.680774328796652</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="12">
         <v>51.433697589627926</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="12">
         <v>43.409368736792423</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="12">
         <v>31.740140413309955</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="12">
         <v>28.94451088455056</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="12">
         <v>22.024662785484026</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="12">
         <v>14.267617212396773</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="12">
         <v>14.778619534247351</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="12">
         <v>14.029577911075274</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="12">
         <v>18.8</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="12">
         <v>23.758244663001044</v>
       </c>
-      <c r="S30" s="37">
+      <c r="S30" s="12">
         <v>19.945481087558658</v>
       </c>
-      <c r="T30" s="37">
+      <c r="T30" s="12">
         <v>20.396452079475392</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="U30" s="12">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="12">
         <v>48.708185613648588</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="12">
         <v>37.931553813927593</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="12">
         <v>38.33463619585136</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="12">
         <v>40.639754074948065</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="12">
         <v>44.16969494757889</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="12">
         <v>50.553915555212974</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="12">
         <v>42.660818605433128</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="12">
         <v>30.494416878480461</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="12">
         <v>28.438702897823607</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="12">
         <v>21.810871896719039</v>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="12">
         <v>12.948414919324932</v>
       </c>
-      <c r="O31" s="16">
+      <c r="O31" s="12">
         <v>15.256250012211552</v>
       </c>
-      <c r="P31" s="16">
+      <c r="P31" s="12">
         <v>14.136273808213584</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="12">
         <v>18.899999999999999</v>
       </c>
-      <c r="R31" s="16">
+      <c r="R31" s="12">
         <v>23.600989554960133</v>
       </c>
-      <c r="S31" s="37">
+      <c r="S31" s="12">
         <v>20.799187962023481</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="12">
         <v>20.655435559889604</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="U31" s="12">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="12">
         <v>44.295394408336584</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="12">
         <v>36.913060085846247</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="12">
         <v>38.245331717166891</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="12">
         <v>43.246261432263722</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="12">
         <v>45.2407499534715</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="12">
         <v>52.418829921890676</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="12">
         <v>44.228326041983919</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="12">
         <v>33.102942270087709</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="12">
         <v>29.489510141633829</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="12">
         <v>22.264452734141326</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="12">
         <v>15.723494620754009</v>
       </c>
-      <c r="O32" s="16">
+      <c r="O32" s="12">
         <v>14.253421863029283</v>
       </c>
-      <c r="P32" s="16">
+      <c r="P32" s="12">
         <v>13.910068203555255</v>
       </c>
-      <c r="Q32" s="16">
+      <c r="Q32" s="12">
         <v>18.7</v>
       </c>
-      <c r="R32" s="16">
+      <c r="R32" s="12">
         <v>23.928051635532135</v>
       </c>
-      <c r="S32" s="37">
+      <c r="S32" s="12">
         <v>19.013188474520234</v>
       </c>
-      <c r="T32" s="37">
+      <c r="T32" s="12">
         <v>20.117912106064367</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="U32" s="12">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="12">
         <v>35.25905281064211</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="12">
         <v>42.972123081253251</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="12">
         <v>33.003964492164805</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="12">
         <v>42.338833276680255</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="12">
         <v>50.172706455002995</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="12">
         <v>39.574780355782721</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="12">
         <v>23.057182049490603</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="12">
         <v>19.048344075891784</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="12">
         <v>21.481514210162892</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="12">
         <v>18.115850908998514</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="12">
         <v>20.679702753300546</v>
       </c>
-      <c r="O33" s="16">
+      <c r="O33" s="12">
         <v>22.085933924873434</v>
       </c>
-      <c r="P33" s="16">
+      <c r="P33" s="12">
         <v>13.290366478193151</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="Q33" s="12">
         <v>12.5</v>
       </c>
-      <c r="R33" s="16">
+      <c r="R33" s="12">
         <v>23.479873624436866</v>
       </c>
-      <c r="S33" s="37">
+      <c r="S33" s="12">
         <v>23.919779113642239</v>
       </c>
-      <c r="T33" s="37">
+      <c r="T33" s="12">
         <v>23.188885535955222</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="U33" s="12">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="12">
         <v>35.524400738676341</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="12">
         <v>45.403420335985643</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="12">
         <v>35.67372171666905</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="12">
         <v>44.324841323157756</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="12">
         <v>51.365667230180513</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="12">
         <v>42.155403417412046</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="12">
         <v>23.320678028402405</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="12">
         <v>19.717988374234295</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="12">
         <v>22.565254965961532</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="12">
         <v>19.131642435267874</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N34" s="12">
         <v>21.405379816313594</v>
       </c>
-      <c r="O34" s="16">
+      <c r="O34" s="12">
         <v>23.802663209890316</v>
       </c>
-      <c r="P34" s="16">
+      <c r="P34" s="12">
         <v>13.968630674154097</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="12">
         <v>12.1</v>
       </c>
-      <c r="R34" s="16">
+      <c r="R34" s="12">
         <v>24.191255182099319</v>
       </c>
-      <c r="S34" s="37">
+      <c r="S34" s="12">
         <v>23.962040711070269</v>
       </c>
-      <c r="T34" s="37">
+      <c r="T34" s="12">
         <v>23.078628487453106</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="U34" s="12">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="12">
         <v>34.937966325921565</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="12">
         <v>40.025342396149952</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="12">
         <v>29.757564599462217</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="12">
         <v>40.090317720015314</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="12">
         <v>48.834976975707399</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="12">
         <v>36.737399067049523</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="12">
         <v>22.797195558030481</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="12">
         <v>18.388950301669212</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="12">
         <v>20.402520679941826</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="12">
         <v>17.094741091820271</v>
       </c>
-      <c r="N35" s="16">
+      <c r="N35" s="12">
         <v>19.940922159102712</v>
       </c>
-      <c r="O35" s="16">
+      <c r="O35" s="12">
         <v>20.340711553536092</v>
       </c>
-      <c r="P35" s="16">
+      <c r="P35" s="12">
         <v>12.593673786232706</v>
       </c>
-      <c r="Q35" s="16">
+      <c r="Q35" s="12">
         <v>12.9</v>
       </c>
-      <c r="R35" s="16">
+      <c r="R35" s="12">
         <v>22.759796314587014</v>
       </c>
-      <c r="S35" s="37">
+      <c r="S35" s="12">
         <v>23.876854008981983</v>
       </c>
-      <c r="T35" s="37">
+      <c r="T35" s="12">
         <v>23.300729383023359</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="U35" s="12">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="12">
         <v>14.980993583120011</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="12">
         <v>15.782630902499408</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="12">
         <v>21.239380737813143</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="12">
         <v>21.868453296842812</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="12">
         <v>28.620908105782696</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="12">
         <v>16.57176566926892</v>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="12">
         <v>23.615399445075923</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="12">
         <v>21.576153857674697</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="12">
         <v>24.813850564692189</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="12">
         <v>30.306456532698682</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="12">
         <v>33.300588375307939</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="12">
         <v>15.569903165791542</v>
       </c>
-      <c r="P36" s="16">
+      <c r="P36" s="12">
         <v>19.096514905237218</v>
       </c>
-      <c r="Q36" s="16">
+      <c r="Q36" s="12">
         <v>25.4</v>
       </c>
-      <c r="R36" s="16">
+      <c r="R36" s="12">
         <v>27.00352039684709</v>
       </c>
-      <c r="S36" s="37">
+      <c r="S36" s="12">
         <v>26.113584517813127</v>
       </c>
-      <c r="T36" s="37">
+      <c r="T36" s="12">
         <v>26.600808028614065</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="12">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="12">
         <v>13.3231770085488</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="12">
         <v>14.947408502944862</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="12">
         <v>20.612282631289872</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="12">
         <v>21.810233831843821</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="12">
         <v>31.580794338047511</v>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="12">
         <v>16.336951373050013</v>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="12">
         <v>23.536874783143453</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="12">
         <v>20.781078549530967</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="12">
         <v>24.231370244694812</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="12">
         <v>29.796795629524667</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="12">
         <v>32.331249850946065</v>
       </c>
-      <c r="O37" s="16">
+      <c r="O37" s="12">
         <v>15.460808768934939</v>
       </c>
-      <c r="P37" s="16">
+      <c r="P37" s="12">
         <v>19.149801807626279</v>
       </c>
-      <c r="Q37" s="16">
+      <c r="Q37" s="12">
         <v>24.3</v>
       </c>
-      <c r="R37" s="16">
+      <c r="R37" s="12">
         <v>26.49991066711625</v>
       </c>
-      <c r="S37" s="37">
+      <c r="S37" s="12">
         <v>25.651528441631889</v>
       </c>
-      <c r="T37" s="37">
+      <c r="T37" s="12">
         <v>26.440501693813694</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="U37" s="12">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="12">
         <v>16.816017468582331</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="12">
         <v>16.656432819748947</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="12">
         <v>21.936013645292753</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="12">
         <v>21.932251240884487</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="12">
         <v>25.292385978318809</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="12">
         <v>16.835987101956384</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="12">
         <v>23.697958067349091</v>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="12">
         <v>22.438096680686812</v>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="12">
         <v>25.448531995394273</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="12">
         <v>30.862157141656372</v>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="12">
         <v>34.357577691815081</v>
       </c>
-      <c r="O38" s="16">
+      <c r="O38" s="12">
         <v>15.68880546767458</v>
       </c>
-      <c r="P38" s="16">
+      <c r="P38" s="12">
         <v>19.03737344064535</v>
       </c>
-      <c r="Q38" s="16">
+      <c r="Q38" s="12">
         <v>26.6</v>
       </c>
-      <c r="R38" s="16">
+      <c r="R38" s="12">
         <v>27.572066513890491</v>
       </c>
-      <c r="S38" s="37">
+      <c r="S38" s="12">
         <v>26.620973515499056</v>
       </c>
-      <c r="T38" s="37">
+      <c r="T38" s="12">
         <v>26.779307280034676</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+      <c r="U38" s="12">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="B39" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="12">
         <v>5.0050408474612667</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="12">
         <v>15.199877458936328</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="12">
         <v>13.244358948423123</v>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="12">
         <v>7.8936298235279043</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="12">
         <v>18.412319077539543</v>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="12">
         <v>21.39425343514112</v>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="12">
         <v>20.37419545157174</v>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="12">
         <v>17.559795089461929</v>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="12">
         <v>23.54181329822454</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="12">
         <v>9.7814403969714476</v>
       </c>
-      <c r="N39" s="16">
+      <c r="N39" s="12">
         <v>15.895976592336902</v>
       </c>
-      <c r="O39" s="16">
+      <c r="O39" s="12">
         <v>15.431849180748594</v>
       </c>
-      <c r="P39" s="16">
+      <c r="P39" s="12">
         <v>11.923173213098794</v>
       </c>
-      <c r="Q39" s="16">
+      <c r="Q39" s="12">
         <v>16.8</v>
       </c>
-      <c r="R39" s="16">
+      <c r="R39" s="12">
         <v>35.769118603355516</v>
       </c>
-      <c r="S39" s="37">
+      <c r="S39" s="12">
         <v>35.676666099583812</v>
       </c>
-      <c r="T39" s="37">
+      <c r="T39" s="12">
         <v>32.389629740110649</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="U39" s="12">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="12">
         <v>4.9910703183897471</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="12">
         <v>14.580407995723835</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="12">
         <v>12.694536401949772</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="12">
         <v>7.3022704780706356</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="12">
         <v>17.12627348202502</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="12">
         <v>19.902241350915418</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="12">
         <v>18.389801845083543</v>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="12">
         <v>15.75684747748228</v>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="12">
         <v>22.249203888313041</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="12">
         <v>8.8993788797454574</v>
       </c>
-      <c r="N40" s="16">
+      <c r="N40" s="12">
         <v>14.320885005874089</v>
       </c>
-      <c r="O40" s="16">
+      <c r="O40" s="12">
         <v>14.746660640556426</v>
       </c>
-      <c r="P40" s="16">
+      <c r="P40" s="12">
         <v>10.945122024518023</v>
       </c>
-      <c r="Q40" s="16">
+      <c r="Q40" s="12">
         <v>16.399999999999999</v>
       </c>
-      <c r="R40" s="16">
+      <c r="R40" s="12">
         <v>35.037028356467729</v>
       </c>
-      <c r="S40" s="37">
+      <c r="S40" s="12">
         <v>34.026766685280904</v>
       </c>
-      <c r="T40" s="37">
+      <c r="T40" s="12">
         <v>31.71205247152805</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="U40" s="12">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="12">
         <v>5.0223457020442774</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="12">
         <v>15.98971335888681</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="12">
         <v>13.950362693192776</v>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="12">
         <v>8.6542146318471769</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="12">
         <v>20.038086648531461</v>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="12">
         <v>23.294374049448368</v>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="12">
         <v>22.845597238166345</v>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="12">
         <v>19.854367582381908</v>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="12">
         <v>25.206391335765652</v>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="12">
         <v>10.893360919362737</v>
       </c>
-      <c r="N41" s="16">
+      <c r="N41" s="12">
         <v>17.858219329297828</v>
       </c>
-      <c r="O41" s="16">
+      <c r="O41" s="12">
         <v>16.325680533022233</v>
       </c>
-      <c r="P41" s="16">
+      <c r="P41" s="12">
         <v>13.205043717586292</v>
       </c>
-      <c r="Q41" s="16">
+      <c r="Q41" s="12">
         <v>17.3</v>
       </c>
-      <c r="R41" s="16">
+      <c r="R41" s="12">
         <v>36.714712776303102</v>
       </c>
-      <c r="S41" s="37">
+      <c r="S41" s="12">
         <v>37.792274390474752</v>
       </c>
-      <c r="T41" s="37">
+      <c r="T41" s="12">
         <v>33.231499210635427</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="U41" s="12">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="12">
         <v>0</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="12">
         <v>0</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="12">
         <v>0</v>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="12">
         <v>0</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="12">
         <v>0</v>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="12">
         <v>0</v>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="12">
         <v>40.875892692669147</v>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="12">
         <v>33.42178613184317</v>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="12">
         <v>38.278868442020823</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="12">
         <v>24.59943985776184</v>
       </c>
-      <c r="N42" s="16">
+      <c r="N42" s="12">
         <v>33.489020691882608</v>
       </c>
-      <c r="O42" s="16">
+      <c r="O42" s="12">
         <v>35.470047966126785</v>
       </c>
-      <c r="P42" s="16">
+      <c r="P42" s="12">
         <v>20.664792285937565</v>
       </c>
-      <c r="Q42" s="16">
+      <c r="Q42" s="12">
         <v>14.7</v>
       </c>
-      <c r="R42" s="16">
+      <c r="R42" s="12">
         <v>28.585005142864613</v>
       </c>
-      <c r="S42" s="37">
+      <c r="S42" s="12">
         <v>26.602385500795538</v>
       </c>
-      <c r="T42" s="37">
+      <c r="T42" s="12">
         <v>13.872134221368512</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="U42" s="12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="12">
         <v>0</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="12">
         <v>0</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="12">
         <v>0</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="12">
         <v>0</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="12">
         <v>0</v>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="12">
         <v>0</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="12">
         <v>40.214976654346749</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="12">
         <v>31.961883196169364</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="12">
         <v>35.847234240268811</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="12">
         <v>23.18714858505685</v>
       </c>
-      <c r="N43" s="16">
+      <c r="N43" s="12">
         <v>30.88827139481976</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O43" s="12">
         <v>33.896959570732115</v>
       </c>
-      <c r="P43" s="16">
+      <c r="P43" s="12">
         <v>19.658727502190441</v>
       </c>
-      <c r="Q43" s="16">
+      <c r="Q43" s="12">
         <v>14.7</v>
       </c>
-      <c r="R43" s="16">
+      <c r="R43" s="12">
         <v>27.745516596290607</v>
       </c>
-      <c r="S43" s="37">
+      <c r="S43" s="12">
         <v>25.585637135242425</v>
       </c>
-      <c r="T43" s="37">
+      <c r="T43" s="12">
         <v>14.562707317462859</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="U43" s="12">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="13">
         <v>0</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="13">
         <v>0</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="13">
         <v>0</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="13">
         <v>0</v>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="13">
         <v>0</v>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="13">
         <v>0</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="13">
         <v>41.620641890921341</v>
       </c>
-      <c r="K44" s="17">
+      <c r="K44" s="13">
         <v>35.041317754766766</v>
       </c>
-      <c r="L44" s="17">
+      <c r="L44" s="13">
         <v>41.029123148407564</v>
       </c>
-      <c r="M44" s="17">
+      <c r="M44" s="13">
         <v>26.170218976651135</v>
       </c>
-      <c r="N44" s="17">
+      <c r="N44" s="13">
         <v>36.383303207045699</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="13">
         <v>37.273729754326382</v>
       </c>
-      <c r="P44" s="17">
+      <c r="P44" s="13">
         <v>21.814125473305914</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="13">
         <v>14.8</v>
       </c>
-      <c r="R44" s="17">
+      <c r="R44" s="13">
         <v>29.549901683892372</v>
       </c>
-      <c r="S44" s="38">
+      <c r="S44" s="13">
         <v>27.750206810614948</v>
       </c>
-      <c r="T44" s="38">
+      <c r="T44" s="13">
         <v>13.080583219648313</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
+      <c r="U44" s="13">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="19"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="5"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19"/>
-      <c r="O50" s="19"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
